--- a/design/templates/generated/Western/HUMAN_SETTLEMENTS_LANDSLIDE_WES_V1_upload_template.xlsx
+++ b/design/templates/generated/Western/HUMAN_SETTLEMENTS_LANDSLIDE_WES_V1_upload_template.xlsx
@@ -7,8 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2020-2025" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2025-2030" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2021-2025" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-2030" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WEIGHTS" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_META" sheetId="5" state="hidden" r:id="rId5"/>
@@ -559,7 +559,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RAW DATA 2020-2025 - Human Settlements Sector - Landslide - Western Province   [profile HUMAN_SETTLEMENTS_LANDSLIDE_WES_V1]   |   Enter RAW values only - the system normalizes.</t>
+          <t>RAW DATA 2021-2025 - Human Settlements Sector - Landslide - Western Province   [profile HUMAN_SETTLEMENTS_LANDSLIDE_WES_V1]   |   Enter RAW values only - the system normalizes.</t>
         </is>
       </c>
     </row>
@@ -786,7 +786,7 @@
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E4" s="6" t="n">
         <v>2025</v>
@@ -829,7 +829,7 @@
       </c>
       <c r="R4" s="6" t="inlineStr">
         <is>
-          <t>Dept. report 2020-2025</t>
+          <t>Dept. report 2021-2025</t>
         </is>
       </c>
       <c r="S4" s="6" t="inlineStr">
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>WES-001</t>
+          <t>CO1</t>
         </is>
       </c>
       <c r="B5" s="7" t="inlineStr">
@@ -855,7 +855,7 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E5" s="7" t="n">
         <v>2025</v>
@@ -878,7 +878,7 @@
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>WES-002</t>
+          <t>CO2</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
@@ -892,7 +892,7 @@
         </is>
       </c>
       <c r="D6" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E6" s="7" t="n">
         <v>2025</v>
@@ -915,7 +915,7 @@
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>WES-003</t>
+          <t>CO3</t>
         </is>
       </c>
       <c r="B7" s="7" t="inlineStr">
@@ -929,7 +929,7 @@
         </is>
       </c>
       <c r="D7" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E7" s="7" t="n">
         <v>2025</v>
@@ -952,7 +952,7 @@
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>WES-004</t>
+          <t>CO4</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
@@ -966,7 +966,7 @@
         </is>
       </c>
       <c r="D8" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E8" s="7" t="n">
         <v>2025</v>
@@ -989,7 +989,7 @@
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>WES-005</t>
+          <t>CO5</t>
         </is>
       </c>
       <c r="B9" s="7" t="inlineStr">
@@ -1003,7 +1003,7 @@
         </is>
       </c>
       <c r="D9" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E9" s="7" t="n">
         <v>2025</v>
@@ -1026,7 +1026,7 @@
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>WES-006</t>
+          <t>CO6</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
@@ -1040,7 +1040,7 @@
         </is>
       </c>
       <c r="D10" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E10" s="7" t="n">
         <v>2025</v>
@@ -1063,7 +1063,7 @@
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>WES-007</t>
+          <t>CO7</t>
         </is>
       </c>
       <c r="B11" s="7" t="inlineStr">
@@ -1077,7 +1077,7 @@
         </is>
       </c>
       <c r="D11" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E11" s="7" t="n">
         <v>2025</v>
@@ -1100,7 +1100,7 @@
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>WES-008</t>
+          <t>CO8</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
@@ -1114,7 +1114,7 @@
         </is>
       </c>
       <c r="D12" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E12" s="7" t="n">
         <v>2025</v>
@@ -1137,7 +1137,7 @@
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>WES-009</t>
+          <t>CO9</t>
         </is>
       </c>
       <c r="B13" s="7" t="inlineStr">
@@ -1151,7 +1151,7 @@
         </is>
       </c>
       <c r="D13" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E13" s="7" t="n">
         <v>2025</v>
@@ -1174,7 +1174,7 @@
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>WES-010</t>
+          <t>CO10</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
@@ -1188,7 +1188,7 @@
         </is>
       </c>
       <c r="D14" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E14" s="7" t="n">
         <v>2025</v>
@@ -1211,7 +1211,7 @@
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
         <is>
-          <t>WES-011</t>
+          <t>CO11</t>
         </is>
       </c>
       <c r="B15" s="7" t="inlineStr">
@@ -1225,7 +1225,7 @@
         </is>
       </c>
       <c r="D15" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E15" s="7" t="n">
         <v>2025</v>
@@ -1248,7 +1248,7 @@
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>WES-012</t>
+          <t>CO12</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
@@ -1262,7 +1262,7 @@
         </is>
       </c>
       <c r="D16" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E16" s="7" t="n">
         <v>2025</v>
@@ -1285,7 +1285,7 @@
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t>WES-013</t>
+          <t>CO13</t>
         </is>
       </c>
       <c r="B17" s="7" t="inlineStr">
@@ -1299,7 +1299,7 @@
         </is>
       </c>
       <c r="D17" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E17" s="7" t="n">
         <v>2025</v>
@@ -1322,7 +1322,7 @@
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
         <is>
-          <t>WES-014</t>
+          <t>GP1</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
@@ -1336,7 +1336,7 @@
         </is>
       </c>
       <c r="D18" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E18" s="7" t="n">
         <v>2025</v>
@@ -1359,7 +1359,7 @@
     <row r="19">
       <c r="A19" s="7" t="inlineStr">
         <is>
-          <t>WES-015</t>
+          <t>GP2</t>
         </is>
       </c>
       <c r="B19" s="7" t="inlineStr">
@@ -1373,7 +1373,7 @@
         </is>
       </c>
       <c r="D19" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E19" s="7" t="n">
         <v>2025</v>
@@ -1396,7 +1396,7 @@
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
         <is>
-          <t>WES-016</t>
+          <t>GP3</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
@@ -1410,7 +1410,7 @@
         </is>
       </c>
       <c r="D20" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E20" s="7" t="n">
         <v>2025</v>
@@ -1433,7 +1433,7 @@
     <row r="21">
       <c r="A21" s="7" t="inlineStr">
         <is>
-          <t>WES-017</t>
+          <t>GP4</t>
         </is>
       </c>
       <c r="B21" s="7" t="inlineStr">
@@ -1447,7 +1447,7 @@
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E21" s="7" t="n">
         <v>2025</v>
@@ -1470,7 +1470,7 @@
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
         <is>
-          <t>WES-018</t>
+          <t>GP5</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
@@ -1484,7 +1484,7 @@
         </is>
       </c>
       <c r="D22" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E22" s="7" t="n">
         <v>2025</v>
@@ -1507,7 +1507,7 @@
     <row r="23">
       <c r="A23" s="7" t="inlineStr">
         <is>
-          <t>WES-019</t>
+          <t>GP6</t>
         </is>
       </c>
       <c r="B23" s="7" t="inlineStr">
@@ -1521,7 +1521,7 @@
         </is>
       </c>
       <c r="D23" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E23" s="7" t="n">
         <v>2025</v>
@@ -1544,7 +1544,7 @@
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
         <is>
-          <t>WES-020</t>
+          <t>GP7</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
@@ -1558,7 +1558,7 @@
         </is>
       </c>
       <c r="D24" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E24" s="7" t="n">
         <v>2025</v>
@@ -1581,7 +1581,7 @@
     <row r="25">
       <c r="A25" s="7" t="inlineStr">
         <is>
-          <t>WES-021</t>
+          <t>GP8</t>
         </is>
       </c>
       <c r="B25" s="7" t="inlineStr">
@@ -1595,7 +1595,7 @@
         </is>
       </c>
       <c r="D25" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E25" s="7" t="n">
         <v>2025</v>
@@ -1618,7 +1618,7 @@
     <row r="26">
       <c r="A26" s="7" t="inlineStr">
         <is>
-          <t>WES-022</t>
+          <t>GP9</t>
         </is>
       </c>
       <c r="B26" s="7" t="inlineStr">
@@ -1632,7 +1632,7 @@
         </is>
       </c>
       <c r="D26" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E26" s="7" t="n">
         <v>2025</v>
@@ -1655,7 +1655,7 @@
     <row r="27">
       <c r="A27" s="7" t="inlineStr">
         <is>
-          <t>WES-023</t>
+          <t>GP10</t>
         </is>
       </c>
       <c r="B27" s="7" t="inlineStr">
@@ -1669,7 +1669,7 @@
         </is>
       </c>
       <c r="D27" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E27" s="7" t="n">
         <v>2025</v>
@@ -1692,7 +1692,7 @@
     <row r="28">
       <c r="A28" s="7" t="inlineStr">
         <is>
-          <t>WES-024</t>
+          <t>GP11</t>
         </is>
       </c>
       <c r="B28" s="7" t="inlineStr">
@@ -1706,7 +1706,7 @@
         </is>
       </c>
       <c r="D28" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E28" s="7" t="n">
         <v>2025</v>
@@ -1729,7 +1729,7 @@
     <row r="29">
       <c r="A29" s="7" t="inlineStr">
         <is>
-          <t>WES-025</t>
+          <t>GP12</t>
         </is>
       </c>
       <c r="B29" s="7" t="inlineStr">
@@ -1743,7 +1743,7 @@
         </is>
       </c>
       <c r="D29" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E29" s="7" t="n">
         <v>2025</v>
@@ -1766,7 +1766,7 @@
     <row r="30">
       <c r="A30" s="7" t="inlineStr">
         <is>
-          <t>WES-026</t>
+          <t>GP13</t>
         </is>
       </c>
       <c r="B30" s="7" t="inlineStr">
@@ -1780,7 +1780,7 @@
         </is>
       </c>
       <c r="D30" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E30" s="7" t="n">
         <v>2025</v>
@@ -1803,7 +1803,7 @@
     <row r="31">
       <c r="A31" s="7" t="inlineStr">
         <is>
-          <t>WES-027</t>
+          <t>KT1</t>
         </is>
       </c>
       <c r="B31" s="7" t="inlineStr">
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="D31" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E31" s="7" t="n">
         <v>2025</v>
@@ -1840,7 +1840,7 @@
     <row r="32">
       <c r="A32" s="7" t="inlineStr">
         <is>
-          <t>WES-028</t>
+          <t>KT2</t>
         </is>
       </c>
       <c r="B32" s="7" t="inlineStr">
@@ -1854,7 +1854,7 @@
         </is>
       </c>
       <c r="D32" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E32" s="7" t="n">
         <v>2025</v>
@@ -1877,7 +1877,7 @@
     <row r="33">
       <c r="A33" s="7" t="inlineStr">
         <is>
-          <t>WES-029</t>
+          <t>KT3</t>
         </is>
       </c>
       <c r="B33" s="7" t="inlineStr">
@@ -1891,7 +1891,7 @@
         </is>
       </c>
       <c r="D33" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E33" s="7" t="n">
         <v>2025</v>
@@ -1914,7 +1914,7 @@
     <row r="34">
       <c r="A34" s="7" t="inlineStr">
         <is>
-          <t>WES-030</t>
+          <t>KT4</t>
         </is>
       </c>
       <c r="B34" s="7" t="inlineStr">
@@ -1928,7 +1928,7 @@
         </is>
       </c>
       <c r="D34" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E34" s="7" t="n">
         <v>2025</v>
@@ -1951,7 +1951,7 @@
     <row r="35">
       <c r="A35" s="7" t="inlineStr">
         <is>
-          <t>WES-031</t>
+          <t>KT5</t>
         </is>
       </c>
       <c r="B35" s="7" t="inlineStr">
@@ -1965,7 +1965,7 @@
         </is>
       </c>
       <c r="D35" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E35" s="7" t="n">
         <v>2025</v>
@@ -1988,7 +1988,7 @@
     <row r="36">
       <c r="A36" s="7" t="inlineStr">
         <is>
-          <t>WES-032</t>
+          <t>KT6</t>
         </is>
       </c>
       <c r="B36" s="7" t="inlineStr">
@@ -2002,7 +2002,7 @@
         </is>
       </c>
       <c r="D36" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E36" s="7" t="n">
         <v>2025</v>
@@ -2025,7 +2025,7 @@
     <row r="37">
       <c r="A37" s="7" t="inlineStr">
         <is>
-          <t>WES-033</t>
+          <t>KT7</t>
         </is>
       </c>
       <c r="B37" s="7" t="inlineStr">
@@ -2039,7 +2039,7 @@
         </is>
       </c>
       <c r="D37" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E37" s="7" t="n">
         <v>2025</v>
@@ -2062,7 +2062,7 @@
     <row r="38">
       <c r="A38" s="7" t="inlineStr">
         <is>
-          <t>WES-034</t>
+          <t>KT8</t>
         </is>
       </c>
       <c r="B38" s="7" t="inlineStr">
@@ -2076,7 +2076,7 @@
         </is>
       </c>
       <c r="D38" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E38" s="7" t="n">
         <v>2025</v>
@@ -2099,7 +2099,7 @@
     <row r="39">
       <c r="A39" s="7" t="inlineStr">
         <is>
-          <t>WES-035</t>
+          <t>KT9</t>
         </is>
       </c>
       <c r="B39" s="7" t="inlineStr">
@@ -2113,7 +2113,7 @@
         </is>
       </c>
       <c r="D39" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E39" s="7" t="n">
         <v>2025</v>
@@ -2136,7 +2136,7 @@
     <row r="40">
       <c r="A40" s="7" t="inlineStr">
         <is>
-          <t>WES-036</t>
+          <t>KT10</t>
         </is>
       </c>
       <c r="B40" s="7" t="inlineStr">
@@ -2150,7 +2150,7 @@
         </is>
       </c>
       <c r="D40" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E40" s="7" t="n">
         <v>2025</v>
@@ -2173,7 +2173,7 @@
     <row r="41">
       <c r="A41" s="7" t="inlineStr">
         <is>
-          <t>WES-037</t>
+          <t>KT11</t>
         </is>
       </c>
       <c r="B41" s="7" t="inlineStr">
@@ -2187,7 +2187,7 @@
         </is>
       </c>
       <c r="D41" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E41" s="7" t="n">
         <v>2025</v>
@@ -2210,7 +2210,7 @@
     <row r="42">
       <c r="A42" s="7" t="inlineStr">
         <is>
-          <t>WES-038</t>
+          <t>KT12</t>
         </is>
       </c>
       <c r="B42" s="7" t="inlineStr">
@@ -2224,7 +2224,7 @@
         </is>
       </c>
       <c r="D42" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E42" s="7" t="n">
         <v>2025</v>
@@ -2247,7 +2247,7 @@
     <row r="43">
       <c r="A43" s="7" t="inlineStr">
         <is>
-          <t>WES-039</t>
+          <t>KT13</t>
         </is>
       </c>
       <c r="B43" s="7" t="inlineStr">
@@ -2261,7 +2261,7 @@
         </is>
       </c>
       <c r="D43" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E43" s="7" t="n">
         <v>2025</v>
@@ -2284,7 +2284,7 @@
     <row r="44">
       <c r="A44" s="7" t="inlineStr">
         <is>
-          <t>WES-040</t>
+          <t>KT14</t>
         </is>
       </c>
       <c r="B44" s="7" t="inlineStr">
@@ -2298,7 +2298,7 @@
         </is>
       </c>
       <c r="D44" s="7" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E44" s="7" t="n">
         <v>2025</v>
@@ -2319,7 +2319,6 @@
       <c r="S44" s="8" t="n"/>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="0" formatRows="1" sort="1"/>
   <mergeCells count="1">
     <mergeCell ref="A1:S1"/>
   </mergeCells>
@@ -2365,7 +2364,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RAW DATA 2025-2030 - Human Settlements Sector - Landslide - Western Province   [profile HUMAN_SETTLEMENTS_LANDSLIDE_WES_V1]   |   Enter RAW values only - the system normalizes.</t>
+          <t>RAW DATA 2026-2030 - Human Settlements Sector - Landslide - Western Province   [profile HUMAN_SETTLEMENTS_LANDSLIDE_WES_V1]   |   Enter RAW values only - the system normalizes.</t>
         </is>
       </c>
     </row>
@@ -2592,7 +2591,7 @@
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E4" s="6" t="n">
         <v>2030</v>
@@ -2635,7 +2634,7 @@
       </c>
       <c r="R4" s="6" t="inlineStr">
         <is>
-          <t>Dept. report 2025-2030</t>
+          <t>Dept. report 2026-2030</t>
         </is>
       </c>
       <c r="S4" s="6" t="inlineStr">
@@ -2647,7 +2646,7 @@
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>WES-001</t>
+          <t>CO1</t>
         </is>
       </c>
       <c r="B5" s="7" t="inlineStr">
@@ -2661,7 +2660,7 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E5" s="7" t="n">
         <v>2030</v>
@@ -2684,7 +2683,7 @@
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>WES-002</t>
+          <t>CO2</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
@@ -2698,7 +2697,7 @@
         </is>
       </c>
       <c r="D6" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E6" s="7" t="n">
         <v>2030</v>
@@ -2721,7 +2720,7 @@
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>WES-003</t>
+          <t>CO3</t>
         </is>
       </c>
       <c r="B7" s="7" t="inlineStr">
@@ -2735,7 +2734,7 @@
         </is>
       </c>
       <c r="D7" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E7" s="7" t="n">
         <v>2030</v>
@@ -2758,7 +2757,7 @@
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>WES-004</t>
+          <t>CO4</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
@@ -2772,7 +2771,7 @@
         </is>
       </c>
       <c r="D8" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E8" s="7" t="n">
         <v>2030</v>
@@ -2795,7 +2794,7 @@
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>WES-005</t>
+          <t>CO5</t>
         </is>
       </c>
       <c r="B9" s="7" t="inlineStr">
@@ -2809,7 +2808,7 @@
         </is>
       </c>
       <c r="D9" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E9" s="7" t="n">
         <v>2030</v>
@@ -2832,7 +2831,7 @@
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>WES-006</t>
+          <t>CO6</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
@@ -2846,7 +2845,7 @@
         </is>
       </c>
       <c r="D10" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E10" s="7" t="n">
         <v>2030</v>
@@ -2869,7 +2868,7 @@
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>WES-007</t>
+          <t>CO7</t>
         </is>
       </c>
       <c r="B11" s="7" t="inlineStr">
@@ -2883,7 +2882,7 @@
         </is>
       </c>
       <c r="D11" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E11" s="7" t="n">
         <v>2030</v>
@@ -2906,7 +2905,7 @@
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>WES-008</t>
+          <t>CO8</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
@@ -2920,7 +2919,7 @@
         </is>
       </c>
       <c r="D12" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E12" s="7" t="n">
         <v>2030</v>
@@ -2943,7 +2942,7 @@
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>WES-009</t>
+          <t>CO9</t>
         </is>
       </c>
       <c r="B13" s="7" t="inlineStr">
@@ -2957,7 +2956,7 @@
         </is>
       </c>
       <c r="D13" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E13" s="7" t="n">
         <v>2030</v>
@@ -2980,7 +2979,7 @@
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>WES-010</t>
+          <t>CO10</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
@@ -2994,7 +2993,7 @@
         </is>
       </c>
       <c r="D14" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E14" s="7" t="n">
         <v>2030</v>
@@ -3017,7 +3016,7 @@
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
         <is>
-          <t>WES-011</t>
+          <t>CO11</t>
         </is>
       </c>
       <c r="B15" s="7" t="inlineStr">
@@ -3031,7 +3030,7 @@
         </is>
       </c>
       <c r="D15" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E15" s="7" t="n">
         <v>2030</v>
@@ -3054,7 +3053,7 @@
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>WES-012</t>
+          <t>CO12</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
@@ -3068,7 +3067,7 @@
         </is>
       </c>
       <c r="D16" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E16" s="7" t="n">
         <v>2030</v>
@@ -3091,7 +3090,7 @@
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t>WES-013</t>
+          <t>CO13</t>
         </is>
       </c>
       <c r="B17" s="7" t="inlineStr">
@@ -3105,7 +3104,7 @@
         </is>
       </c>
       <c r="D17" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E17" s="7" t="n">
         <v>2030</v>
@@ -3128,7 +3127,7 @@
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
         <is>
-          <t>WES-014</t>
+          <t>GP1</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
@@ -3142,7 +3141,7 @@
         </is>
       </c>
       <c r="D18" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E18" s="7" t="n">
         <v>2030</v>
@@ -3165,7 +3164,7 @@
     <row r="19">
       <c r="A19" s="7" t="inlineStr">
         <is>
-          <t>WES-015</t>
+          <t>GP2</t>
         </is>
       </c>
       <c r="B19" s="7" t="inlineStr">
@@ -3179,7 +3178,7 @@
         </is>
       </c>
       <c r="D19" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E19" s="7" t="n">
         <v>2030</v>
@@ -3202,7 +3201,7 @@
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
         <is>
-          <t>WES-016</t>
+          <t>GP3</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
@@ -3216,7 +3215,7 @@
         </is>
       </c>
       <c r="D20" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E20" s="7" t="n">
         <v>2030</v>
@@ -3239,7 +3238,7 @@
     <row r="21">
       <c r="A21" s="7" t="inlineStr">
         <is>
-          <t>WES-017</t>
+          <t>GP4</t>
         </is>
       </c>
       <c r="B21" s="7" t="inlineStr">
@@ -3253,7 +3252,7 @@
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E21" s="7" t="n">
         <v>2030</v>
@@ -3276,7 +3275,7 @@
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
         <is>
-          <t>WES-018</t>
+          <t>GP5</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
@@ -3290,7 +3289,7 @@
         </is>
       </c>
       <c r="D22" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E22" s="7" t="n">
         <v>2030</v>
@@ -3313,7 +3312,7 @@
     <row r="23">
       <c r="A23" s="7" t="inlineStr">
         <is>
-          <t>WES-019</t>
+          <t>GP6</t>
         </is>
       </c>
       <c r="B23" s="7" t="inlineStr">
@@ -3327,7 +3326,7 @@
         </is>
       </c>
       <c r="D23" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E23" s="7" t="n">
         <v>2030</v>
@@ -3350,7 +3349,7 @@
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
         <is>
-          <t>WES-020</t>
+          <t>GP7</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
@@ -3364,7 +3363,7 @@
         </is>
       </c>
       <c r="D24" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E24" s="7" t="n">
         <v>2030</v>
@@ -3387,7 +3386,7 @@
     <row r="25">
       <c r="A25" s="7" t="inlineStr">
         <is>
-          <t>WES-021</t>
+          <t>GP8</t>
         </is>
       </c>
       <c r="B25" s="7" t="inlineStr">
@@ -3401,7 +3400,7 @@
         </is>
       </c>
       <c r="D25" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E25" s="7" t="n">
         <v>2030</v>
@@ -3424,7 +3423,7 @@
     <row r="26">
       <c r="A26" s="7" t="inlineStr">
         <is>
-          <t>WES-022</t>
+          <t>GP9</t>
         </is>
       </c>
       <c r="B26" s="7" t="inlineStr">
@@ -3438,7 +3437,7 @@
         </is>
       </c>
       <c r="D26" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E26" s="7" t="n">
         <v>2030</v>
@@ -3461,7 +3460,7 @@
     <row r="27">
       <c r="A27" s="7" t="inlineStr">
         <is>
-          <t>WES-023</t>
+          <t>GP10</t>
         </is>
       </c>
       <c r="B27" s="7" t="inlineStr">
@@ -3475,7 +3474,7 @@
         </is>
       </c>
       <c r="D27" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E27" s="7" t="n">
         <v>2030</v>
@@ -3498,7 +3497,7 @@
     <row r="28">
       <c r="A28" s="7" t="inlineStr">
         <is>
-          <t>WES-024</t>
+          <t>GP11</t>
         </is>
       </c>
       <c r="B28" s="7" t="inlineStr">
@@ -3512,7 +3511,7 @@
         </is>
       </c>
       <c r="D28" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E28" s="7" t="n">
         <v>2030</v>
@@ -3535,7 +3534,7 @@
     <row r="29">
       <c r="A29" s="7" t="inlineStr">
         <is>
-          <t>WES-025</t>
+          <t>GP12</t>
         </is>
       </c>
       <c r="B29" s="7" t="inlineStr">
@@ -3549,7 +3548,7 @@
         </is>
       </c>
       <c r="D29" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E29" s="7" t="n">
         <v>2030</v>
@@ -3572,7 +3571,7 @@
     <row r="30">
       <c r="A30" s="7" t="inlineStr">
         <is>
-          <t>WES-026</t>
+          <t>GP13</t>
         </is>
       </c>
       <c r="B30" s="7" t="inlineStr">
@@ -3586,7 +3585,7 @@
         </is>
       </c>
       <c r="D30" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E30" s="7" t="n">
         <v>2030</v>
@@ -3609,7 +3608,7 @@
     <row r="31">
       <c r="A31" s="7" t="inlineStr">
         <is>
-          <t>WES-027</t>
+          <t>KT1</t>
         </is>
       </c>
       <c r="B31" s="7" t="inlineStr">
@@ -3623,7 +3622,7 @@
         </is>
       </c>
       <c r="D31" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E31" s="7" t="n">
         <v>2030</v>
@@ -3646,7 +3645,7 @@
     <row r="32">
       <c r="A32" s="7" t="inlineStr">
         <is>
-          <t>WES-028</t>
+          <t>KT2</t>
         </is>
       </c>
       <c r="B32" s="7" t="inlineStr">
@@ -3660,7 +3659,7 @@
         </is>
       </c>
       <c r="D32" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E32" s="7" t="n">
         <v>2030</v>
@@ -3683,7 +3682,7 @@
     <row r="33">
       <c r="A33" s="7" t="inlineStr">
         <is>
-          <t>WES-029</t>
+          <t>KT3</t>
         </is>
       </c>
       <c r="B33" s="7" t="inlineStr">
@@ -3697,7 +3696,7 @@
         </is>
       </c>
       <c r="D33" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E33" s="7" t="n">
         <v>2030</v>
@@ -3720,7 +3719,7 @@
     <row r="34">
       <c r="A34" s="7" t="inlineStr">
         <is>
-          <t>WES-030</t>
+          <t>KT4</t>
         </is>
       </c>
       <c r="B34" s="7" t="inlineStr">
@@ -3734,7 +3733,7 @@
         </is>
       </c>
       <c r="D34" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E34" s="7" t="n">
         <v>2030</v>
@@ -3757,7 +3756,7 @@
     <row r="35">
       <c r="A35" s="7" t="inlineStr">
         <is>
-          <t>WES-031</t>
+          <t>KT5</t>
         </is>
       </c>
       <c r="B35" s="7" t="inlineStr">
@@ -3771,7 +3770,7 @@
         </is>
       </c>
       <c r="D35" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E35" s="7" t="n">
         <v>2030</v>
@@ -3794,7 +3793,7 @@
     <row r="36">
       <c r="A36" s="7" t="inlineStr">
         <is>
-          <t>WES-032</t>
+          <t>KT6</t>
         </is>
       </c>
       <c r="B36" s="7" t="inlineStr">
@@ -3808,7 +3807,7 @@
         </is>
       </c>
       <c r="D36" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E36" s="7" t="n">
         <v>2030</v>
@@ -3831,7 +3830,7 @@
     <row r="37">
       <c r="A37" s="7" t="inlineStr">
         <is>
-          <t>WES-033</t>
+          <t>KT7</t>
         </is>
       </c>
       <c r="B37" s="7" t="inlineStr">
@@ -3845,7 +3844,7 @@
         </is>
       </c>
       <c r="D37" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E37" s="7" t="n">
         <v>2030</v>
@@ -3868,7 +3867,7 @@
     <row r="38">
       <c r="A38" s="7" t="inlineStr">
         <is>
-          <t>WES-034</t>
+          <t>KT8</t>
         </is>
       </c>
       <c r="B38" s="7" t="inlineStr">
@@ -3882,7 +3881,7 @@
         </is>
       </c>
       <c r="D38" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E38" s="7" t="n">
         <v>2030</v>
@@ -3905,7 +3904,7 @@
     <row r="39">
       <c r="A39" s="7" t="inlineStr">
         <is>
-          <t>WES-035</t>
+          <t>KT9</t>
         </is>
       </c>
       <c r="B39" s="7" t="inlineStr">
@@ -3919,7 +3918,7 @@
         </is>
       </c>
       <c r="D39" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E39" s="7" t="n">
         <v>2030</v>
@@ -3942,7 +3941,7 @@
     <row r="40">
       <c r="A40" s="7" t="inlineStr">
         <is>
-          <t>WES-036</t>
+          <t>KT10</t>
         </is>
       </c>
       <c r="B40" s="7" t="inlineStr">
@@ -3956,7 +3955,7 @@
         </is>
       </c>
       <c r="D40" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E40" s="7" t="n">
         <v>2030</v>
@@ -3979,7 +3978,7 @@
     <row r="41">
       <c r="A41" s="7" t="inlineStr">
         <is>
-          <t>WES-037</t>
+          <t>KT11</t>
         </is>
       </c>
       <c r="B41" s="7" t="inlineStr">
@@ -3993,7 +3992,7 @@
         </is>
       </c>
       <c r="D41" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E41" s="7" t="n">
         <v>2030</v>
@@ -4016,7 +4015,7 @@
     <row r="42">
       <c r="A42" s="7" t="inlineStr">
         <is>
-          <t>WES-038</t>
+          <t>KT12</t>
         </is>
       </c>
       <c r="B42" s="7" t="inlineStr">
@@ -4030,7 +4029,7 @@
         </is>
       </c>
       <c r="D42" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E42" s="7" t="n">
         <v>2030</v>
@@ -4053,7 +4052,7 @@
     <row r="43">
       <c r="A43" s="7" t="inlineStr">
         <is>
-          <t>WES-039</t>
+          <t>KT13</t>
         </is>
       </c>
       <c r="B43" s="7" t="inlineStr">
@@ -4067,7 +4066,7 @@
         </is>
       </c>
       <c r="D43" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E43" s="7" t="n">
         <v>2030</v>
@@ -4090,7 +4089,7 @@
     <row r="44">
       <c r="A44" s="7" t="inlineStr">
         <is>
-          <t>WES-040</t>
+          <t>KT14</t>
         </is>
       </c>
       <c r="B44" s="7" t="inlineStr">
@@ -4104,7 +4103,7 @@
         </is>
       </c>
       <c r="D44" s="7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E44" s="7" t="n">
         <v>2030</v>
@@ -4125,7 +4124,6 @@
       <c r="S44" s="8" t="n"/>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="0" formatRows="1" sort="1"/>
   <mergeCells count="1">
     <mergeCell ref="A1:S1"/>
   </mergeCells>
@@ -4144,7 +4142,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -4153,6 +4151,7 @@
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="46" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4200,6 +4199,11 @@
           <t>PROPOSED WEIGHT % (read at import)</t>
         </is>
       </c>
+      <c r="G3" s="10" t="inlineStr">
+        <is>
+          <t>basis of the proposal</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="11" t="inlineStr">
@@ -4228,6 +4232,7 @@
       <c r="F4" s="12" t="n">
         <v>20</v>
       </c>
+      <c r="G4" s="11" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="11" t="inlineStr">
@@ -4256,6 +4261,7 @@
       <c r="F5" s="12" t="n">
         <v>50</v>
       </c>
+      <c r="G5" s="11" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="13" t="inlineStr">
@@ -4276,6 +4282,7 @@
       <c r="D6" s="13" t="n"/>
       <c r="E6" s="13" t="n"/>
       <c r="F6" s="12" t="n"/>
+      <c r="G6" s="13" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="11" t="inlineStr">
@@ -4304,6 +4311,7 @@
       <c r="F7" s="12" t="n">
         <v>30</v>
       </c>
+      <c r="G7" s="11" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="11" t="inlineStr">
@@ -4332,6 +4340,7 @@
       <c r="F8" s="12" t="n">
         <v>15</v>
       </c>
+      <c r="G8" s="11" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="13" t="inlineStr">
@@ -4352,6 +4361,7 @@
       <c r="D9" s="13" t="n"/>
       <c r="E9" s="13" t="n"/>
       <c r="F9" s="12" t="n"/>
+      <c r="G9" s="13" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="11" t="inlineStr">
@@ -4380,6 +4390,7 @@
       <c r="F10" s="12" t="n">
         <v>15</v>
       </c>
+      <c r="G10" s="11" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="11" t="inlineStr">
@@ -4408,6 +4419,7 @@
       <c r="F11" s="12" t="n">
         <v>10</v>
       </c>
+      <c r="G11" s="11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="11" t="inlineStr">
@@ -4436,6 +4448,7 @@
       <c r="F12" s="12" t="n">
         <v>20</v>
       </c>
+      <c r="G12" s="11" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="11" t="inlineStr">
@@ -4464,6 +4477,7 @@
       <c r="F13" s="12" t="n">
         <v>10</v>
       </c>
+      <c r="G13" s="11" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="11" t="inlineStr">
@@ -4492,6 +4506,7 @@
       <c r="F14" s="12" t="n">
         <v>10</v>
       </c>
+      <c r="G14" s="11" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="11" t="inlineStr">
@@ -4520,6 +4535,7 @@
       <c r="F15" s="12" t="n">
         <v>10</v>
       </c>
+      <c r="G15" s="11" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="14" t="inlineStr">
@@ -4544,9 +4560,8 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="0" formatRows="1" sort="1"/>
   <mergeCells count="1">
-    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A2:G2"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation sqref="F4 F5 F6 F7 F8 F9 F10 F11 F12 F13 F14 F15" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid weight" error="Weight must be between 0 and 100." type="decimal" operator="between">
@@ -4585,14 +4600,14 @@
     <row r="2">
       <c r="A2" s="16" t="inlineStr">
         <is>
-          <t>Profile: HUMAN_SETTLEMENTS_LANDSLIDE_WES_V1   |   generated 2026-07-29 from FINAL_VARIABLES.xlsx (expert-refined catalog)</t>
+          <t>Profile: HUMAN_SETTLEMENTS_LANDSLIDE_WES_V1   |   generated 2026-09-03 from FINAL_VARIABLES.xlsx (expert-refined catalog)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="17" t="inlineStr">
         <is>
-          <t>1. One tab per data period (2020-2025, 2025-2030). Fill the tab matching your dataset's period; skip tabs with no data.</t>
+          <t>1. One tab per data period (2021-2025, 2026-2030). Fill the tab matching your dataset's period; skip tabs with no data.</t>
         </is>
       </c>
     </row>
@@ -4606,14 +4621,14 @@
     <row r="6">
       <c r="A6" s="17" t="inlineStr">
         <is>
-          <t>2b. The year 2025 appears in both tabs. If a year sits in two periods the system uses the LATER period's value, so nothing is counted twice.</t>
+          <t>2b. The two periods are contiguous and do not overlap (changed 2026-09-03 at the Central panel's request - the old 2020-2025 / 2025-2030 pair shared the year 2025 and needed a tie-break). Every year belongs to exactly one tab.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="17" t="inlineStr">
-        <is>
-          <t>3. Edit ONLY the yellow cells. Division codes, names, district and the period columns are pre-filled and locked.</t>
+      <c r="A7" s="18" t="inlineStr">
+        <is>
+          <t>3. REVIEW COPY - nothing is locked. The yellow cells are still where data belongs, but every cell, header and tab can be changed so the panel can mark up structure as well as values. Return the marked-up file; the finalised version will be re-issued locked for collection.</t>
         </is>
       </c>
     </row>
@@ -4627,7 +4642,7 @@
     <row r="9">
       <c r="A9" s="17" t="inlineStr">
         <is>
-          <t>5. Do not add, remove, rename or reorder columns or tabs. Files with changed structure are rejected on import.</t>
+          <t>5. Structural changes ARE invited in this review copy - add, rename or reorder columns and note what you changed. This file is NOT importable; the locked re-issue is.</t>
         </is>
       </c>
     </row>
@@ -5057,7 +5072,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5141,80 +5156,104 @@
     <row r="8">
       <c r="A8" s="17" t="inlineStr">
         <is>
-          <t>generated</t>
+          <t>protection</t>
         </is>
       </c>
       <c r="B8" s="17" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>unlocked-review</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="17" t="inlineStr">
         <is>
-          <t>dsd_level</t>
+          <t>panel_overrides</t>
         </is>
       </c>
       <c r="B9" s="17" t="inlineStr">
         <is>
-          <t>DS_DIVISION</t>
+          <t>0 add, 0 retire</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="17" t="inlineStr">
         <is>
-          <t>periods</t>
+          <t>generated</t>
         </is>
       </c>
       <c r="B10" s="17" t="inlineStr">
         <is>
-          <t>2020-2025|2025-2030</t>
+          <t>2026-09-03</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="17" t="inlineStr">
         <is>
-          <t>n_variables</t>
-        </is>
-      </c>
-      <c r="B11" s="17" t="n">
-        <v>12</v>
+          <t>dsd_level</t>
+        </is>
+      </c>
+      <c r="B11" s="17" t="inlineStr">
+        <is>
+          <t>DS_DIVISION</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="17" t="inlineStr">
         <is>
-          <t>period_rule_default</t>
+          <t>periods</t>
         </is>
       </c>
       <c r="B12" s="17" t="inlineStr">
         <is>
-          <t>average (typical year); 2025 -&gt; latest period wins</t>
+          <t>2021-2025|2026-2030</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="17" t="inlineStr">
         <is>
-          <t>period_aggregation</t>
-        </is>
-      </c>
-      <c r="B13" s="17" t="inlineStr">
-        <is>
-          <t>CUTTING_FAILURES_EARTH_SLIPS_2000_TO_2023=fixed_window|LANDSLIDE_EVENTS_1974_TO_2023=fixed_window|LANDSLIDE_HAZARD_INDEX=fixed_window|VERY_WET_DAYS=average|BUILDINGS_LANDSLIDE_PRONE_AREA_HIGH_MODERATE=average|LANDSLIDE_AFFECTED_AREA_HIGH_MODERATE=average|LANDSLIDE_AFFECTED_ROAD_LENGTH=average|LANDSLIDE_PRONE_HUMAN_SETTLEMENTS=average|MAXIMUM_LANDSLIDE_AFFECTED_PEOPLE_DURING_1974_TO_2023=max|PUBLIC_HOSPITALS=average|ROAD_DENSITY=average|SCHOOLS_LANDSLIDE_PRONE_AREA_HIGH_MODERATE=average</t>
-        </is>
+          <t>n_variables</t>
+        </is>
+      </c>
+      <c r="B13" s="17" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="17" t="inlineStr">
         <is>
+          <t>period_rule_default</t>
+        </is>
+      </c>
+      <c r="B14" s="17" t="inlineStr">
+        <is>
+          <t>average (typical year); periods are contiguous, no overlap</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="17" t="inlineStr">
+        <is>
+          <t>period_aggregation</t>
+        </is>
+      </c>
+      <c r="B15" s="17" t="inlineStr">
+        <is>
+          <t>CUTTING_FAILURES_EARTH_SLIPS_2000_TO_2023=fixed_window|LANDSLIDE_EVENTS_1974_TO_2023=fixed_window|LANDSLIDE_HAZARD_INDEX=fixed_window|VERY_WET_DAYS=average|BUILDINGS_LANDSLIDE_PRONE_AREA_HIGH_MODERATE=average|LANDSLIDE_AFFECTED_AREA_HIGH_MODERATE=average|LANDSLIDE_AFFECTED_ROAD_LENGTH=average|LANDSLIDE_PRONE_HUMAN_SETTLEMENTS=average|MAXIMUM_LANDSLIDE_AFFECTED_PEOPLE_DURING_1974_TO_2023=max|PUBLIC_HOSPITALS=average|ROAD_DENSITY=average|SCHOOLS_LANDSLIDE_PRONE_AREA_HIGH_MODERATE=average</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="17" t="inlineStr">
+        <is>
           <t>expected_columns</t>
         </is>
       </c>
-      <c r="B14" s="17" t="inlineStr">
+      <c r="B16" s="17" t="inlineStr">
         <is>
           <t>DS_CODE|DS_DIVISION|DISTRICT|YEAR_START|YEAR_END|CUTTING_FAILURES_EARTH_SLIPS_2000_TO_2023|LANDSLIDE_EVENTS_1974_TO_2023|LANDSLIDE_HAZARD_INDEX|VERY_WET_DAYS|BUILDINGS_LANDSLIDE_PRONE_AREA_HIGH_MODERATE|LANDSLIDE_AFFECTED_AREA_HIGH_MODERATE|LANDSLIDE_AFFECTED_ROAD_LENGTH|LANDSLIDE_PRONE_HUMAN_SETTLEMENTS|MAXIMUM_LANDSLIDE_AFFECTED_PEOPLE_DURING_1974_TO_2023|PUBLIC_HOSPITALS|ROAD_DENSITY|SCHOOLS_LANDSLIDE_PRONE_AREA_HIGH_MODERATE|DATA_SOURCE|NOTES</t>
         </is>

--- a/design/templates/generated/Western/HUMAN_SETTLEMENTS_LANDSLIDE_WES_V1_upload_template.xlsx
+++ b/design/templates/generated/Western/HUMAN_SETTLEMENTS_LANDSLIDE_WES_V1_upload_template.xlsx
@@ -4600,7 +4600,7 @@
     <row r="2">
       <c r="A2" s="16" t="inlineStr">
         <is>
-          <t>Profile: HUMAN_SETTLEMENTS_LANDSLIDE_WES_V1   |   generated 2026-09-03 from FINAL_VARIABLES.xlsx (expert-refined catalog)</t>
+          <t>Profile: HUMAN_SETTLEMENTS_LANDSLIDE_WES_V1   |   generated 2026-09-14 from FINAL_VARIABLES.xlsx (expert-refined catalog)</t>
         </is>
       </c>
     </row>
@@ -4626,9 +4626,9 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="18" t="inlineStr">
-        <is>
-          <t>3. REVIEW COPY - nothing is locked. The yellow cells are still where data belongs, but every cell, header and tab can be changed so the panel can mark up structure as well as values. Return the marked-up file; the finalised version will be re-issued locked for collection.</t>
+      <c r="A7" s="17" t="inlineStr">
+        <is>
+          <t>3. The yellow cells are where data belongs. Division codes, names, district and the period columns are pre-filled - change one only to correct a genuine error. Nothing in this file is protected, so please treat that as the instruction it is; the importer checks those columns and will refuse what it cannot match.</t>
         </is>
       </c>
     </row>
@@ -4642,7 +4642,7 @@
     <row r="9">
       <c r="A9" s="17" t="inlineStr">
         <is>
-          <t>5. Structural changes ARE invited in this review copy - add, rename or reorder columns and note what you changed. This file is NOT importable; the locked re-issue is.</t>
+          <t>5. Do not add, remove, rename or reorder columns or tabs. Excel will now let you - the sheet is not protected - but the importer will not: the hidden _META tab states this file's column contract and a file whose structure has changed is refused, naming what changed. Nothing loads partially, so a rejected file loads nothing at all.</t>
         </is>
       </c>
     </row>
@@ -5161,7 +5161,7 @@
       </c>
       <c r="B8" s="17" t="inlineStr">
         <is>
-          <t>unlocked-review</t>
+          <t>locked</t>
         </is>
       </c>
     </row>
@@ -5185,7 +5185,7 @@
       </c>
       <c r="B10" s="17" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-14</t>
         </is>
       </c>
     </row>
